--- a/UTCUTS/A1_Outputs/reference_works/A-O_Parametrization_REF.xlsx
+++ b/UTCUTS/A1_Outputs/reference_works/A-O_Parametrization_REF.xlsx
@@ -39979,5 +39979,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36CE644E-3932-4E47-ACF5-36983795B020}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0800C7F-4C8F-4F29-88C7-4E3F4DF95136}"/>
 </file>